--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1228 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1169,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,903 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>124.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1118,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1227,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1338,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1371,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1482,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1593,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -1671,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -1704,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1782,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -1815,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1839,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1859,13 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1893,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1926,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1950,33 +2002,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2087,7 +2143,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2198,7 +2254,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2309,7 +2365,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2420,7 +2476,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2531,7 +2587,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2642,7 +2698,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2753,7 +2809,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2864,7 +2920,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2981,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2975,7 +3031,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3092,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3086,7 +3142,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3203,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3197,7 +3253,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3314,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3308,7 +3364,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3425,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3419,7 +3475,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3536,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3534,7 +3590,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3651,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3649,7 +3705,1264 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2171,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,33 +2232,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2426,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,7 +2473,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2504,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2537,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,33 +2573,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2615,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2648,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2672,17 +2692,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2692,13 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2726,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2759,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2783,33 +2811,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2837,32 +2869,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2870,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2894,17 +2930,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2914,13 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2948,32 +2988,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2981,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3005,33 +3049,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3107,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -3092,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3116,17 +3168,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3136,13 +3188,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -3170,32 +3226,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3203,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3227,17 +3287,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3247,13 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3590,7 +3654,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3705,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3931,7 +3995,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4046,7 +4110,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4161,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4276,7 +4340,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4391,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4506,7 +4570,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4631,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4678,7 +4742,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4732,7 +4796,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4857,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4847,7 +4911,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4972,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4962,6 +5026,914 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
           <t>9/27</t>
         </is>
       </c>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3117,24 +3117,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -3345,32 +3345,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3402,17 +3406,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3422,13 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3600,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,7 +3647,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3654,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3682,32 +3690,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3715,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3739,17 +3751,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3759,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -3797,32 +3809,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3830,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3854,33 +3870,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -3908,32 +3928,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3941,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3965,17 +3989,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3985,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4023,32 +4047,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4056,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4080,37 +4108,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4166,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4171,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4195,17 +4227,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4215,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4253,32 +4285,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4286,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4310,37 +4346,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4404,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4401,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,17 +4465,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4445,17 +4485,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4555,7 +4595,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4570,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4638,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq49，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4631,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4639,10 +4679,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4742,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4796,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4911,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4972,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5026,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5141,7 +5193,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5591,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5593,7 +5645,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5706,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5765,7 +5817,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5819,7 +5871,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5932,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5934,7 +5986,808 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>19/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>22/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>20/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>16/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,18 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,7 +2256,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,13 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2484,7 +2492,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3079,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3547,7 +3555,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4138,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4176,24 +4184,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4203,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4252,12 +4260,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4434,12 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4441,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4610,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4651,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq49，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq41推进至seq60，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4671,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4722,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4733,7 +4741,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4761,32 +4769,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -4794,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4818,17 +4830,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4838,17 +4850,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4876,32 +4888,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4909,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4933,37 +4949,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4991,32 +5007,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5024,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5048,17 +5068,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5068,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5106,32 +5126,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -5139,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5163,17 +5187,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5183,17 +5207,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5221,32 +5245,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -5254,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5278,33 +5306,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5332,32 +5364,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5365,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5389,17 +5425,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5409,7 +5445,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5419,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5447,32 +5483,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5480,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5504,17 +5544,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5524,13 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5645,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5745,7 +5789,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5756,7 +5800,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5871,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5986,7 +6030,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6101,7 +6145,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6212,7 +6256,7 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6327,7 +6371,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6442,7 +6486,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6547,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6557,7 +6601,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6662,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6672,7 +6716,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6777,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6787,7 +6831,681 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,13 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,18 +3548,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3789,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4564,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4618,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4860,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5098,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5255,24 +5263,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5282,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5493,24 +5501,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5520,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5577,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5602,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5635,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,17 +5671,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5679,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5717,32 +5729,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5750,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,17 +5790,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5794,13 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5828,32 +5848,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5861,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5885,37 +5909,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5943,32 +5967,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5976,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6000,37 +6028,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6058,32 +6086,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -6091,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6115,17 +6147,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6135,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6173,32 +6205,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6206,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6230,33 +6266,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6356,7 +6396,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6432,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6486,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6601,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6831,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,7 +7269,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7278,12 +7318,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,7 +7495,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7499,13 +7539,592 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,14 +4258,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6324,32 +6324,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6381,17 +6385,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6401,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6439,32 +6443,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6472,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6496,17 +6504,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6516,7 +6524,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6554,32 +6562,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6587,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,32 +6623,32 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6669,32 +6681,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6702,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,17 +6742,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6746,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6784,32 +6800,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6817,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,37 +6861,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6919,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6932,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6940,10 +6960,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7010,32 +7046,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7043,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7067,17 +7107,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7087,12 +7127,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7158,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7197,7 +7237,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7269,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7779,7 +7819,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7894,7 +7934,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7999,17 +8039,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8128,6 +8168,692 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,14 +5091,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6810,24 +6810,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7165,32 +7165,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,17 +7226,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7242,13 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7276,32 +7284,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -7309,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,17 +7345,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7353,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -7391,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7424,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7468,13 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7502,32 +7522,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7535,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,17 +7583,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7579,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7617,32 +7641,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7650,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,17 +7702,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7694,12 +7722,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7765,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7880,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7995,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8110,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8225,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8279,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8394,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8509,7 +8537,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8619,12 +8647,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8747,22 +8775,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8795,12 +8823,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8814,7 +8842,7 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8839,7 +8867,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8851,6 +8879,581 @@
       <c r="AC71" s="2" t="inlineStr">
         <is>
           <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,14 +3195,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,17 +6643,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,14 +7479,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7651,24 +7651,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7760,32 +7760,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7793,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,17 +7821,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7837,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7875,32 +7879,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7908,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,17 +7940,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7952,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7990,32 +7998,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8023,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8047,17 +8059,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8067,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8105,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8138,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,17 +8178,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8182,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8220,32 +8236,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8253,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8277,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8297,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8335,32 +8355,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8368,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8392,17 +8416,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8412,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8537,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8713,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8828,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8939,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9284,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9338,7 +9362,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9453,7 +9477,927 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>28/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>127.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8474,32 +8474,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8507,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,17 +8535,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8551,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8737,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8963,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9078,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9132,7 +9136,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9308,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9423,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9477,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9592,7 +9596,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9768,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9883,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9937,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9998,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10113,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10228,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10343,7 +10347,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10401,6 +10405,121 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>130.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,14 +3782,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,14 +8312,14 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8365,24 +8365,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8496,12 +8496,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8550,14 +8550,14 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8593,32 +8593,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8626,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,17 +8654,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8670,17 +8674,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8708,32 +8712,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8741,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,37 +8773,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8831,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8856,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,10 +8872,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±2分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -8967,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9049,32 +9073,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -9082,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,17 +9134,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9126,17 +9154,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9312,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9366,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9481,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9596,7 +9624,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9772,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9941,7 +9969,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10117,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10232,7 +10260,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10347,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10409,22 +10437,22 @@
       <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10457,12 +10485,12 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10476,47 +10504,737 @@
       <c r="T85" s="2" t="inlineStr"/>
       <c r="U85" s="2" t="inlineStr">
         <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
           <t>17:20</t>
         </is>
       </c>
-      <c r="V85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W85" s="2" t="inlineStr">
+      <c r="W86" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X85" s="2" t="inlineStr">
+      <c r="X86" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y85" s="2" t="inlineStr">
+      <c r="Y86" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z85" s="2" t="inlineStr">
+      <c r="Z86" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
+      <c r="AA86" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
+      <c r="AB86" s="2" t="inlineStr">
         <is>
           <t>130.3</t>
         </is>
       </c>
-      <c r="AC85" s="2" t="inlineStr">
+      <c r="AC86" s="2" t="inlineStr">
         <is>
           <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8958,32 +8958,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8991,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9015,32 +9019,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9083,24 +9087,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9110,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9149,22 +9153,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9264,7 +9268,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9340,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9422,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9455,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,37 +9487,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9537,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9570,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9606,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9614,17 +9626,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9652,32 +9664,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9685,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,17 +9725,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9729,12 +9745,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9800,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9915,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9954,7 +9970,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9969,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10145,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10260,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10375,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10490,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10544,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10774,7 +10790,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10835,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10950,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11004,7 +11020,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11119,7 +11135,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11234,7 +11250,923 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,14 +2600,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>127.3</t>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,14 +5686,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>127.3</t>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9740,14 +9740,14 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>127.3</t>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9783,32 +9783,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9816,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,37 +9844,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9898,32 +9902,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -9931,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,17 +9963,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9975,17 +9983,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10013,32 +10021,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10046,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10070,37 +10082,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -10128,32 +10140,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10161,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10185,32 +10201,32 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10243,32 +10259,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10276,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10320,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10320,17 +10340,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10473,32 +10493,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10506,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10530,17 +10554,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10550,17 +10574,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10736,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10790,7 +10814,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10966,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11020,7 +11044,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11135,7 +11159,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11250,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11426,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11537,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11652,7 +11676,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11706,7 +11730,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11821,7 +11845,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11997,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12041,17 +12065,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12059,22 +12083,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12107,12 +12131,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12126,47 +12150,852 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W100" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X100" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y100" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z100" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
+      <c r="AB100" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
         </is>
       </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>22/29</t>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>28/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,22 +5567,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,17 +5810,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8793,17 +8793,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,17 +9273,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10727,32 +10727,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10760,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,37 +10788,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10842,32 +10846,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -10875,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10899,17 +10907,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10919,12 +10927,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10957,32 +10965,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10990,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11014,17 +11026,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11034,17 +11046,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11072,32 +11084,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11105,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11129,17 +11145,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11149,17 +11165,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11203,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11220,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11244,17 +11264,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11264,17 +11284,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11335,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11417,12 +11437,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq62，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -11450,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11458,10 +11478,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
       <c r="S93" s="2" t="inlineStr"/>
-      <c r="T93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11528,32 +11560,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11561,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11585,17 +11621,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11605,12 +11641,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11643,32 +11679,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11676,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11700,17 +11740,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11720,17 +11760,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11873,32 +11913,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11906,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11930,17 +11974,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11950,17 +11994,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12065,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12136,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12251,7 +12295,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12366,7 +12410,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12481,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12596,7 +12640,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12711,7 +12755,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12765,7 +12809,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12826,7 +12870,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12880,7 +12924,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12941,7 +12985,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12995,7 +13039,237 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-浦东35路.xlsx
+++ b/data/export/2026-10-07-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9507,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9745,17 +9745,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11689,24 +11689,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11798,32 +11798,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -11831,7 +11835,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11855,17 +11859,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11875,17 +11879,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11927,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
@@ -11950,7 +11954,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11999,12 +12003,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12032,12 +12036,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12065,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12073,10 +12077,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:00</t>
@@ -12147,32 +12167,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12180,7 +12204,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12204,17 +12228,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12224,12 +12248,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12262,32 +12286,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12295,7 +12323,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,17 +12347,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12339,17 +12367,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12377,12 +12405,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -12410,7 +12438,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12418,10 +12446,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
-      <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
           <t>19:20</t>
@@ -12525,7 +12569,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12607,32 +12651,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12640,7 +12688,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12664,17 +12712,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12684,17 +12732,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12870,7 +12918,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12924,7 +12972,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12985,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13100,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13215,7 +13263,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
